--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104666_W24.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104666_W24.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5981</v>
+        <v>6.3708</v>
       </c>
       <c r="E2" t="n">
-        <v>3.3857</v>
+        <v>4.1261</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2124</v>
+        <v>2.2447</v>
       </c>
       <c r="G2" t="n">
-        <v>2.5184</v>
+        <v>2.5078</v>
       </c>
       <c r="H2" t="n">
-        <v>1.5296</v>
+        <v>1.528</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9888</v>
+        <v>0.9798</v>
       </c>
       <c r="J2" t="n">
-        <v>2.8828</v>
+        <v>2.8465</v>
       </c>
       <c r="K2" t="n">
-        <v>1.3263</v>
+        <v>1.3133</v>
       </c>
       <c r="L2" t="n">
-        <v>1.5565</v>
+        <v>1.5333</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.3644</v>
+        <v>-0.3387</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2033</v>
+        <v>0.2148</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.5676</v>
+        <v>-0.5535</v>
       </c>
       <c r="P2" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3992</v>
+        <v>1.1801</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5444</v>
+        <v>1.3283</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1452</v>
+        <v>-0.1482</v>
       </c>
       <c r="V2" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W2" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. ARANITOVIC</t>
+          <t>A. KURUCS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.9035</v>
+        <v>4.1145</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7753</v>
+        <v>0.3659</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1282</v>
+        <v>3.7486</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5383</v>
+        <v>1.1937</v>
       </c>
       <c r="H3" t="n">
-        <v>1.4126</v>
+        <v>-0.2958</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.8743</v>
+        <v>1.4895</v>
       </c>
       <c r="J3" t="n">
-        <v>2.6831</v>
+        <v>0.0994</v>
       </c>
       <c r="K3" t="n">
-        <v>1.8702</v>
+        <v>-0.5106000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8129</v>
+        <v>0.61</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.1447</v>
+        <v>1.0942</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4576</v>
+        <v>0.2148</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.6871</v>
+        <v>0.8794999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>2.2683</v>
+        <v>1.8211</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>3.4025</v>
+        <v>2.9592</v>
       </c>
       <c r="S3" t="n">
-        <v>2.8039</v>
+        <v>1.0998</v>
       </c>
       <c r="T3" t="n">
-        <v>2.0657</v>
+        <v>1.2469</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7382</v>
+        <v>-0.1471</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.7071</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.8678</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. SAKHO</t>
+          <t>A. ARANITOVIC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.6603</v>
+        <v>4.1023</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8501</v>
+        <v>3.5862</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8102</v>
+        <v>0.5161</v>
       </c>
       <c r="G4" t="n">
-        <v>3.5345</v>
+        <v>0.5414</v>
       </c>
       <c r="H4" t="n">
-        <v>3.2093</v>
+        <v>1.4158</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3253</v>
+        <v>-0.8744</v>
       </c>
       <c r="J4" t="n">
-        <v>3.8058</v>
+        <v>2.6578</v>
       </c>
       <c r="K4" t="n">
-        <v>3.6192</v>
+        <v>1.8616</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1866</v>
+        <v>0.7962</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2712</v>
+        <v>-2.1164</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4099</v>
+        <v>-0.4458</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1387</v>
+        <v>-1.6706</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.2763</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>2.2683</v>
+        <v>3.4145</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3791</v>
+        <v>1.9871</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3126</v>
+        <v>1.9088</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0665</v>
+        <v>0.0784</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.2534</v>
+        <v>-0.7025</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2534</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. KURUCS</t>
+          <t>J. SAKHO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.457</v>
+        <v>3.1958</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2758</v>
+        <v>2.3576</v>
       </c>
       <c r="F5" t="n">
-        <v>3.1812</v>
+        <v>0.8381999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1969</v>
+        <v>3.5325</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2958</v>
+        <v>3.2</v>
       </c>
       <c r="I5" t="n">
-        <v>1.4927</v>
+        <v>0.3325</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1272</v>
+        <v>3.7887</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.4991</v>
+        <v>3.6025</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6263</v>
+        <v>0.1862</v>
       </c>
       <c r="M5" t="n">
-        <v>1.0697</v>
+        <v>-0.2562</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2033</v>
+        <v>-0.4025</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8663999999999999</v>
+        <v>0.1463</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8147</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R5" t="n">
-        <v>2.9488</v>
+        <v>2.2763</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4455</v>
+        <v>0.9105</v>
       </c>
       <c r="T5" t="n">
-        <v>1.1221</v>
+        <v>0.8452</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6766</v>
+        <v>0.0653</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1607</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. DIBBA</t>
+          <t>F. ALONSO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8736</v>
+        <v>0.1405</v>
       </c>
       <c r="E6" t="n">
-        <v>1.4724</v>
+        <v>0.9804</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5987</v>
+        <v>-0.84</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2</v>
+        <v>-0.3376</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2958</v>
+        <v>1.4279</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4958</v>
+        <v>-1.7655</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7858000000000001</v>
+        <v>0.4749</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1141</v>
+        <v>1.2131</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6717</v>
+        <v>-0.7382</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5858</v>
+        <v>-0.8125</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4099</v>
+        <v>0.2148</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1759</v>
+        <v>-1.0273</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2268</v>
+        <v>0.6829</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>1.361</v>
+        <v>1.8211</v>
       </c>
       <c r="S6" t="n">
-        <v>1.5395</v>
+        <v>-0.5203</v>
       </c>
       <c r="T6" t="n">
-        <v>1.8207</v>
+        <v>0.0809</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2813</v>
+        <v>-0.6012</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.0927</v>
+        <v>0.3155</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.5628</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0927</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. QUINTELA</t>
+          <t>B. DIBBA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3903</v>
+        <v>-0.2948</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0171</v>
+        <v>0.2841</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3732</v>
+        <v>-0.5789</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3359</v>
+        <v>0.2049</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>-0.2958</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3359</v>
+        <v>0.5007</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0373</v>
+        <v>0.7769</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.1067</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0373</v>
+        <v>0.6703</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3732</v>
+        <v>-0.572</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-0.4025</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3732</v>
+        <v>-0.1695</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.2276</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.3658</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7168</v>
+        <v>0.3622</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7168</v>
+        <v>0.6454</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0.2832</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.7712</v>
+        <v>-1.0895</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.7712</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="8">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5458</v>
+        <v>-0.3136</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1662</v>
+        <v>-0.081</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3796</v>
+        <v>-0.2326</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4887</v>
+        <v>0.4769</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.6491</v>
+        <v>-1.6622</v>
       </c>
       <c r="I8" t="n">
-        <v>2.1378</v>
+        <v>2.1391</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5709</v>
+        <v>0.5463</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.7428</v>
+        <v>-1.7624</v>
       </c>
       <c r="L8" t="n">
-        <v>2.3136</v>
+        <v>2.3087</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0822</v>
+        <v>-0.0694</v>
       </c>
       <c r="N8" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.1002</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1759</v>
+        <v>-0.1695</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5789</v>
+        <v>-0.3368</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4386</v>
+        <v>0.5596</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.0174</v>
+        <v>-0.8964</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2249</v>
+        <v>0.2292</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.8678</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. ALONSO</t>
+          <t>E. QUINTELA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6728</v>
+        <v>-0.8629</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1368</v>
+        <v>-0.4906</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8096</v>
+        <v>-0.3724</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3234</v>
+        <v>-0.3351</v>
       </c>
       <c r="H9" t="n">
-        <v>1.4359</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.7593</v>
+        <v>-0.3351</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5128</v>
+        <v>0.0372</v>
       </c>
       <c r="K9" t="n">
-        <v>1.2326</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7198</v>
+        <v>0.0372</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8362000000000001</v>
+        <v>-0.3724</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2033</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0395</v>
+        <v>-0.3724</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6805</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8147</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.3513</v>
+        <v>0.2462</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8166</v>
+        <v>0.2462</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5347</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3214</v>
+        <v>-0.7739</v>
       </c>
       <c r="W9" t="n">
-        <v>1.5748</v>
+        <v>-0.7739</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. BRANKOVIC</t>
+          <t>D. MAVRA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7931</v>
+        <v>-0.9775</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9847</v>
+        <v>-2.0806</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1916</v>
+        <v>1.1031</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.2864</v>
+        <v>1.0442</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4312</v>
+        <v>1.9482</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.8551</v>
+        <v>-0.904</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.2343</v>
+        <v>2.4725</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6345</v>
+        <v>2.0782</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5998</v>
+        <v>0.3943</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.0521</v>
+        <v>-1.4282</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2033</v>
+        <v>-0.13</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.2554</v>
+        <v>-1.2982</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6805</v>
+        <v>-4.325</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>-6.8289</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8147</v>
+        <v>2.5039</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5198</v>
+        <v>1.3715</v>
       </c>
       <c r="T10" t="n">
-        <v>1.7693</v>
+        <v>1.1864</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2495</v>
+        <v>0.1851</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.7071</v>
+        <v>0.9317</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.3856</v>
+        <v>1.0895</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.3214</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>K. COOK</t>
+          <t>D. BRANKOVIC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.974</v>
+        <v>-1.3443</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9082</v>
+        <v>-1.4133</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0658</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.2885</v>
+        <v>-2.2896</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.2885</v>
+        <v>-0.4444</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>-1.8452</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.769</v>
+        <v>-1.2627</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.769</v>
+        <v>-0.6592</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-0.6035</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.5195</v>
+        <v>-1.027</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5195</v>
+        <v>0.2148</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>-1.2417</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>0.6829</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.8211</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1391</v>
+        <v>0.965</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1391</v>
+        <v>1.3746</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>-0.4096</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.5463</v>
+        <v>-0.7025</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.387</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5463</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. MAVRA</t>
+          <t>K. COOK</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.0693</v>
+        <v>-1.7368</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.9143</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>0.845</v>
+        <v>-1.0618</v>
       </c>
       <c r="G12" t="n">
-        <v>1.0567</v>
+        <v>-1.2895</v>
       </c>
       <c r="H12" t="n">
-        <v>1.9656</v>
+        <v>-1.2895</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9089</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2.5137</v>
+        <v>-0.7724</v>
       </c>
       <c r="K12" t="n">
-        <v>2.1086</v>
+        <v>-0.7724</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4051</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.457</v>
+        <v>-0.5171</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1431</v>
+        <v>-0.5171</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.314</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>-4.3098</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-6.805</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.4952</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2519</v>
+        <v>0.0975</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2843</v>
+        <v>0.0975</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0324</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>0.9320000000000001</v>
+        <v>-0.5447</v>
       </c>
       <c r="W12" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.1607</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>12.0472</v>
+        <v>12.394</v>
       </c>
       <c r="E13" t="n">
-        <v>6.905599999999999</v>
+        <v>6.9599</v>
       </c>
       <c r="F13" t="n">
-        <v>5.1417</v>
+        <v>5.434</v>
       </c>
       <c r="G13" t="n">
-        <v>5.299300000000001</v>
+        <v>5.249600000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>5.5926</v>
+        <v>5.5322</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2931000000000001</v>
+        <v>-0.2826000000000002</v>
       </c>
       <c r="J13" t="n">
-        <v>11.9161</v>
+        <v>11.6651</v>
       </c>
       <c r="K13" t="n">
-        <v>6.625600000000001</v>
+        <v>6.4708</v>
       </c>
       <c r="L13" t="n">
-        <v>5.290399999999999</v>
+        <v>5.194500000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-6.616599999999999</v>
+        <v>-6.415700000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.0331</v>
+        <v>-0.9385000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>-5.5835</v>
+        <v>-5.476900000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2683</v>
+        <v>2.276299999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-18.1468</v>
+        <v>-18.2107</v>
       </c>
       <c r="R13" t="n">
-        <v>20.415</v>
+        <v>20.4869</v>
       </c>
       <c r="S13" t="n">
-        <v>6.986400000000001</v>
+        <v>7.3628</v>
       </c>
       <c r="T13" t="n">
-        <v>9.118799999999998</v>
+        <v>9.5198</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.1324</v>
+        <v>-2.1569</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.5068</v>
+        <v>-2.4944</v>
       </c>
       <c r="W13" t="n">
-        <v>4.0175</v>
+        <v>3.985999999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.5242</v>
+        <v>-6.4803</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.3921</v>
+        <v>3.7209</v>
       </c>
       <c r="E14" t="n">
-        <v>3.6602</v>
+        <v>3.6433</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2681</v>
+        <v>0.0776</v>
       </c>
       <c r="G14" t="n">
-        <v>2.8092</v>
+        <v>2.8129</v>
       </c>
       <c r="H14" t="n">
-        <v>1.9349</v>
+        <v>1.9385</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8743</v>
+        <v>0.8744</v>
       </c>
       <c r="J14" t="n">
-        <v>3.4636</v>
+        <v>3.4439</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9438</v>
+        <v>2.9303</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.6543</v>
+        <v>-0.631</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.0089</v>
+        <v>-0.9918</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3546</v>
+        <v>0.3608</v>
       </c>
       <c r="P14" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.366</v>
+        <v>-0.0512</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1966</v>
+        <v>0.1994</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5626</v>
+        <v>-0.2505</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.6667</v>
+        <v>3.2866</v>
       </c>
       <c r="E15" t="n">
-        <v>3.3028</v>
+        <v>3.8465</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.636</v>
+        <v>-0.5599</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4798</v>
+        <v>0.4851</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.6366</v>
+        <v>-1.6207</v>
       </c>
       <c r="I15" t="n">
-        <v>2.1163</v>
+        <v>2.1059</v>
       </c>
       <c r="J15" t="n">
-        <v>2.6772</v>
+        <v>2.6461</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.5959</v>
+        <v>-0.6</v>
       </c>
       <c r="L15" t="n">
-        <v>3.273</v>
+        <v>3.2462</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.1974</v>
+        <v>-2.161</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0407</v>
+        <v>-1.0207</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.1567</v>
+        <v>-1.1403</v>
       </c>
       <c r="P15" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.9738</v>
+        <v>-1.3563</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.747</v>
+        <v>-0.156</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.2267</v>
+        <v>-1.2003</v>
       </c>
       <c r="V15" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="W15" t="n">
-        <v>2.5068</v>
+        <v>2.4945</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6371</v>
+        <v>0.5083</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7155</v>
+        <v>0.1089</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0784</v>
+        <v>0.3995</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4311</v>
+        <v>0.4514</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3058</v>
+        <v>0.3154</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1254</v>
+        <v>0.136</v>
       </c>
       <c r="J16" t="n">
-        <v>1.2405</v>
+        <v>1.2363</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6061</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6344</v>
+        <v>0.633</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8094</v>
+        <v>-0.7849</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3003</v>
+        <v>-0.2879</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.509</v>
+        <v>-0.497</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R16" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S16" t="n">
-        <v>0.206</v>
+        <v>0.0569</v>
       </c>
       <c r="T16" t="n">
-        <v>1.2612</v>
+        <v>0.6756</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.0552</v>
+        <v>-0.6187</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.4822</v>
+        <v>0.4733</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.4822</v>
+        <v>-0.4733</v>
       </c>
     </row>
     <row r="17">
@@ -1735,22 +1735,22 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3354</v>
+        <v>0.3681</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1781</v>
+        <v>0.2102</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1762,13 +1762,13 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -1780,13 +1780,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1781</v>
+        <v>0.2102</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0209</v>
+        <v>0.0523</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1317</v>
+        <v>0.2131</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.878</v>
+        <v>-0.7701</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0097</v>
+        <v>0.9832</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2829</v>
+        <v>-0.2898</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9379</v>
+        <v>0.9364</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.2209</v>
+        <v>-1.2262</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.7388</v>
+        <v>-0.7492</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7966</v>
+        <v>0.7929</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.5354</v>
+        <v>-1.542</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4559</v>
+        <v>0.4593</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1414</v>
+        <v>0.1435</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3145</v>
+        <v>0.3159</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1878</v>
+        <v>0.2753</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1391</v>
+        <v>-0.021</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3269</v>
+        <v>0.2962</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3514</v>
+        <v>-0.6427</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0965</v>
+        <v>-0.2276</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2549</v>
+        <v>-0.4152</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.7793</v>
+        <v>-1.7684</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.459</v>
+        <v>-2.4476</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6797</v>
+        <v>0.6792</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2054</v>
+        <v>-0.2202</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.4342</v>
+        <v>-1.4414</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2287</v>
+        <v>1.2211</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.5738</v>
+        <v>-1.5481</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.0248</v>
+        <v>-1.0062</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.549</v>
+        <v>-0.5419</v>
       </c>
       <c r="P19" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3188</v>
+        <v>-0.6271</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1089</v>
+        <v>-0.0073</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4277</v>
+        <v>-0.6198</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="20">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6591</v>
+        <v>-0.8692</v>
       </c>
       <c r="E20" t="n">
-        <v>2.0263</v>
+        <v>1.3156</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.6854</v>
+        <v>-2.1849</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7187</v>
+        <v>-0.6974</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1777</v>
+        <v>-0.1644</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.541</v>
+        <v>-0.5329</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6956</v>
+        <v>0.6888</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1385</v>
+        <v>0.1379</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.4143</v>
+        <v>-1.3861</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3162</v>
+        <v>-0.3023</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.0981</v>
+        <v>-1.0838</v>
       </c>
       <c r="P20" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4355</v>
+        <v>-0.6758</v>
       </c>
       <c r="T20" t="n">
-        <v>1.3308</v>
+        <v>0.6268</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.7663</v>
+        <v>-1.3027</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="21">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.0265</v>
+        <v>-2.3521</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.1838</v>
+        <v>-2.6225</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1573</v>
+        <v>0.2704</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.8374</v>
+        <v>-4.8423</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.0173</v>
+        <v>-2.0163</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.8202</v>
+        <v>-2.8261</v>
       </c>
       <c r="J21" t="n">
-        <v>-4.2199</v>
+        <v>-4.2414</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.0474</v>
+        <v>-2.0587</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.1725</v>
+        <v>-2.1827</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6176</v>
+        <v>-0.6009</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0301</v>
+        <v>0.0424</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.6433</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S21" t="n">
-        <v>0.07920000000000001</v>
+        <v>0.7665</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0151</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0944</v>
+        <v>0.1884</v>
       </c>
       <c r="V21" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="W21" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.6173</v>
+        <v>-2.9679</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.308</v>
+        <v>-2.2384</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3093</v>
+        <v>-0.7296</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.4637</v>
+        <v>-4.4579</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.4935</v>
+        <v>-3.4898</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.9702</v>
+        <v>-0.9681999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.7577</v>
+        <v>-1.793</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.4138</v>
+        <v>-1.4349</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.344</v>
+        <v>-0.3581</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.706</v>
+        <v>-2.6649</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.0797</v>
+        <v>-2.0549</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6263</v>
+        <v>-0.61</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R22" t="n">
-        <v>3.1757</v>
+        <v>3.1868</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.8606</v>
+        <v>-1.2125</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.08160000000000001</v>
+        <v>0.039</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.779</v>
+        <v>-1.2515</v>
       </c>
       <c r="V22" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="W22" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.8347</v>
+        <v>-3.6075</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.9553</v>
+        <v>-3.8801</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1206</v>
+        <v>0.2726</v>
       </c>
       <c r="G23" t="n">
-        <v>2.3882</v>
+        <v>2.3901</v>
       </c>
       <c r="H23" t="n">
-        <v>1.29</v>
+        <v>1.2923</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0982</v>
+        <v>1.0978</v>
       </c>
       <c r="J23" t="n">
-        <v>2.2353</v>
+        <v>2.2158</v>
       </c>
       <c r="K23" t="n">
-        <v>1.1185</v>
+        <v>1.1064</v>
       </c>
       <c r="L23" t="n">
-        <v>1.1168</v>
+        <v>1.1094</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1529</v>
+        <v>0.1743</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1715</v>
+        <v>0.1859</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.0186</v>
+        <v>-0.0116</v>
       </c>
       <c r="P23" t="n">
-        <v>-4.3098</v>
+        <v>-4.325</v>
       </c>
       <c r="Q23" t="n">
-        <v>-5.6708</v>
+        <v>-5.6908</v>
       </c>
       <c r="R23" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9811</v>
+        <v>-0.7409</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0907</v>
+        <v>0.2111</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.0719</v>
+        <v>-0.952</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.6105</v>
+        <v>-0.6162</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.7213</v>
+        <v>-7.3342</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.5822</v>
+        <v>-4.7676</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.1391</v>
+        <v>-2.5666</v>
       </c>
       <c r="G24" t="n">
-        <v>0.5172</v>
+        <v>0.5088</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.2771</v>
+        <v>-0.2758</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7942</v>
+        <v>0.7846</v>
       </c>
       <c r="J24" t="n">
-        <v>3.2264</v>
+        <v>3.1885</v>
       </c>
       <c r="K24" t="n">
-        <v>0.9209000000000001</v>
+        <v>0.9028</v>
       </c>
       <c r="L24" t="n">
-        <v>2.3055</v>
+        <v>2.2857</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.7092</v>
+        <v>-2.6797</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.198</v>
+        <v>-1.1786</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.5113</v>
+        <v>-1.5011</v>
       </c>
       <c r="P24" t="n">
-        <v>-5.444</v>
+        <v>-5.4632</v>
       </c>
       <c r="Q24" t="n">
-        <v>-7.9391</v>
+        <v>-7.9671</v>
       </c>
       <c r="R24" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.7018</v>
+        <v>-1.2904</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0302</v>
+        <v>-0.1467</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.6716</v>
+        <v>-1.1436</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W24" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-12.0473</v>
+        <v>-9.676600000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.1417</v>
+        <v>-5.4341</v>
       </c>
       <c r="F25" t="n">
-        <v>-6.9055</v>
+        <v>-4.2427</v>
       </c>
       <c r="G25" t="n">
-        <v>-5.2992</v>
+        <v>-5.249599999999998</v>
       </c>
       <c r="H25" t="n">
-        <v>-5.5926</v>
+        <v>-5.532000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2930999999999999</v>
+        <v>0.2824000000000009</v>
       </c>
       <c r="J25" t="n">
-        <v>6.6168</v>
+        <v>6.415600000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>1.0331</v>
+        <v>0.9385999999999997</v>
       </c>
       <c r="L25" t="n">
-        <v>5.5832</v>
+        <v>5.477099999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>-11.9159</v>
+        <v>-11.6651</v>
       </c>
       <c r="N25" t="n">
-        <v>-6.6256</v>
+        <v>-6.4706</v>
       </c>
       <c r="O25" t="n">
-        <v>-5.2903</v>
+        <v>-5.1944</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.268399999999999</v>
+        <v>-2.2764</v>
       </c>
       <c r="Q25" t="n">
-        <v>-20.4149</v>
+        <v>-20.4869</v>
       </c>
       <c r="R25" t="n">
-        <v>18.1466</v>
+        <v>18.2104</v>
       </c>
       <c r="S25" t="n">
-        <v>-6.986499999999999</v>
+        <v>-4.6453</v>
       </c>
       <c r="T25" t="n">
-        <v>2.1325</v>
+        <v>2.1569</v>
       </c>
       <c r="U25" t="n">
-        <v>-9.1188</v>
+        <v>-6.8022</v>
       </c>
       <c r="V25" t="n">
-        <v>2.5066</v>
+        <v>2.4944</v>
       </c>
       <c r="W25" t="n">
-        <v>6.5242</v>
+        <v>6.4803</v>
       </c>
       <c r="X25" t="n">
-        <v>-4.0175</v>
+        <v>-3.9858</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104666_W24.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104666_W24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104666_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104666_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104666_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104666_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104666_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104666_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104666_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104666_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104666_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104666_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104666_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-6.4803</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104666_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104666_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.4733</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104666_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104666_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104666_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104666_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104666_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104666_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104666_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104666_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104666_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-3.9858</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
